--- a/data/trans_orig/IP2902-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37243</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27342</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>52088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74594</t>
+          <t>75345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>32866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78287</t>
+          <t>78271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96881</t>
+          <t>97570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77433</t>
+          <t>76730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96259</t>
+          <t>96371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>160059</t>
+          <t>159866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>187612</t>
+          <t>187350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36112</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54471</t>
+          <t>53620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48258</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>69884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90933</t>
+          <t>90424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>117117</t>
+          <t>117731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37258</t>
+          <t>36236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43431</t>
+          <t>43870</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108817</t>
+          <t>110245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129085</t>
+          <t>129733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110884</t>
+          <t>110162</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133143</t>
+          <t>133416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>227298</t>
+          <t>226074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256634</t>
+          <t>257567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,59%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>45321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41693</t>
+          <t>42701</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>59771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81997</t>
+          <t>81399</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26362</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44227</t>
+          <t>43766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74653</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91802</t>
+          <t>91377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84783</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>166088</t>
+          <t>164709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189814</t>
+          <t>189245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61371</t>
+          <t>61727</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58457</t>
+          <t>57698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83970</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111990</t>
+          <t>112892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28688</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48493</t>
+          <t>49435</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119936</t>
+          <t>119237</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142722</t>
+          <t>143361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118611</t>
+          <t>118398</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>139139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>245149</t>
+          <t>244115</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>276128</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>142679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177498</t>
+          <t>177534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157117</t>
+          <t>158721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193258</t>
+          <t>195439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>310916</t>
+          <t>312500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>361299</t>
+          <t>360328</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>66446</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90879</t>
+          <t>93239</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78337</t>
+          <t>78878</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106384</t>
+          <t>106461</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150722</t>
+          <t>151377</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189952</t>
+          <t>190237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>401969</t>
+          <t>403199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>442491</t>
+          <t>440745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>410571</t>
+          <t>411008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>451712</t>
+          <t>452874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>826628</t>
+          <t>824815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>884332</t>
+          <t>881227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>24579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>42574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>50799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60895</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85841</t>
+          <t>84084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31971</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87220</t>
+          <t>86592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105573</t>
+          <t>105385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84616</t>
+          <t>84701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104554</t>
+          <t>104920</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>177533</t>
+          <t>178881</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205403</t>
+          <t>206616</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52175</t>
+          <t>52058</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>71532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>59933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81786</t>
+          <t>82113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117243</t>
+          <t>118025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147916</t>
+          <t>148867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>30423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26923</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>51020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106973</t>
+          <t>106921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129178</t>
+          <t>129043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119176</t>
+          <t>119114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142616</t>
+          <t>142661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233087</t>
+          <t>231837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>265254</t>
+          <t>264741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>39233</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57227</t>
+          <t>57147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57228</t>
+          <t>56543</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82367</t>
+          <t>81713</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107444</t>
+          <t>107606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25122</t>
+          <t>25877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>15441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29330</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31259</t>
+          <t>31642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50880</t>
+          <t>49591</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77647</t>
+          <t>78750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97775</t>
+          <t>97320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83453</t>
+          <t>84524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103955</t>
+          <t>103888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165956</t>
+          <t>167684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195850</t>
+          <t>196036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49986</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72365</t>
+          <t>72581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65857</t>
+          <t>63742</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88849</t>
+          <t>88155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121957</t>
+          <t>119986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153053</t>
+          <t>152529</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>24325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40980</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27482</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>55337</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79931</t>
+          <t>82112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103547</t>
+          <t>103016</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>128985</t>
+          <t>127671</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81642</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105595</t>
+          <t>106848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>195005</t>
+          <t>193024</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>227556</t>
+          <t>228496</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182270</t>
+          <t>183510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219449</t>
+          <t>222753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212118</t>
+          <t>214237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254953</t>
+          <t>253551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>407196</t>
+          <t>409343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>463469</t>
+          <t>464516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>68087</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107160</t>
+          <t>106403</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>152899</t>
+          <t>155473</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193067</t>
+          <t>194805</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>398306</t>
+          <t>398049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>440979</t>
+          <t>441660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>391947</t>
+          <t>393101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439168</t>
+          <t>436109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>802360</t>
+          <t>802786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>861957</t>
+          <t>865015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38864</t>
+          <t>37725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23417</t>
+          <t>23510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39807</t>
+          <t>40660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49458</t>
+          <t>50473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72969</t>
+          <t>73139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26566</t>
+          <t>26446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28390</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47584</t>
+          <t>47222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73085</t>
+          <t>72980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91578</t>
+          <t>91446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84911</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103686</t>
+          <t>103346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163784</t>
+          <t>163198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>190568</t>
+          <t>191634</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48505</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67765</t>
+          <t>68052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93393</t>
+          <t>92966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>35211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47432</t>
+          <t>48336</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54525</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>77540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127790</t>
+          <t>127929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148081</t>
+          <t>147865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127923</t>
+          <t>128473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152444</t>
+          <t>152226</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262529</t>
+          <t>263630</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293993</t>
+          <t>294267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>43672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46587</t>
+          <t>47147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85760</t>
+          <t>85555</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32818</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18546</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>41116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61349</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83054</t>
+          <t>82845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102014</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88054</t>
+          <t>87370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107632</t>
+          <t>107540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176881</t>
+          <t>175248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203849</t>
+          <t>203477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25059</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>43773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50951</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76017</t>
+          <t>76721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>29197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46762</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41720</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>58102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83174</t>
+          <t>83963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118471</t>
+          <t>118253</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141740</t>
+          <t>140996</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125405</t>
+          <t>124251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146419</t>
+          <t>145768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>252289</t>
+          <t>248688</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282448</t>
+          <t>281231</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121796</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156203</t>
+          <t>155373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121927</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157045</t>
+          <t>155888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253969</t>
+          <t>254897</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>299064</t>
+          <t>300948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>92687</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123823</t>
+          <t>124248</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>132128</t>
+          <t>132961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>200036</t>
+          <t>202845</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>246839</t>
+          <t>244968</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>422892</t>
+          <t>423121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>463413</t>
+          <t>463199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>447788</t>
+          <t>451236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>490310</t>
+          <t>490771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>883189</t>
+          <t>886026</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>940397</t>
+          <t>944300</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2902-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35058</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27457</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43942</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,01%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28283</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21010</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37155</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21699</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36537</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35058</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27311</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>44071</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52088</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>75415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24267</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17468</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32137</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20107</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14191</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27271</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13785</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27348</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>14,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24267</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17247</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32866</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>35650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55869</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>87089</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77345</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97234</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>59,48%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>52,83%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>66,41%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87624</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>78271</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>97570</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>78314</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>96589</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>64,42%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>87089</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76730</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>96371</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>59,48%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159866</t>
+          <t>161417</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>187350</t>
+          <t>187727</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>146414</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>146414</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>146414</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>136014</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>136014</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>136014</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>146414</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>146414</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>146414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59007</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48949</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69675</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>44856</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35775</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53620</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>36279</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>55511</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>59007</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48679</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>69884</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90424</t>
+          <t>90961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>117731</t>
+          <t>118350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -1296,67 +1296,67 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>27859</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>25579</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>19427</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>33436</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19449</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>33893</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>13,46%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>27859</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20784</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36236</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43870</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64556</t>
+          <t>65351</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121847</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>109402</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>132966</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>119610</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>110245</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>129733</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>109692</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>130500</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>121847</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>110162</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>133416</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,38%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226074</t>
+          <t>225410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257567</t>
+          <t>257012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>190045</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>190045</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>190045</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33530</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26136</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42226</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28,85%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36872</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29342</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>45321</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29820</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45140</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>26,99%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33530</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>26383</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>42701</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59771</t>
+          <t>59692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81399</t>
+          <t>82823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18863</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12444</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25936</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>16002</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11523</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22990</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10840</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22291</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18863</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13114</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25736</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93972</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>84425</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103389</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>83740</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74109</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91377</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>75257</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>91927</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>93972</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84447</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102721</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>64,2%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164709</t>
+          <t>164524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189245</t>
+          <t>190640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -1978,52 +1978,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>146365</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>146365</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>146365</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>136614</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>136614</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>136614</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>146365</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>146365</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>146365</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47414</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36920</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56430</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>50180</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39600</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>61727</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>40855</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>61001</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>25,3%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>47414</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38407</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>57698</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83491</t>
+          <t>83660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112892</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21146</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14693</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29082</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16629</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11167</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24474</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11003</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24301</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>21146</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>15165</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>28568</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29340</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49435</t>
+          <t>48265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>129243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>118662</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139880</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>65,34%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>59,99%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>70,72%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>131515</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119237</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>143361</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>119771</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>142752</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>66,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>60,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>72,29%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>129243</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>118398</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139139</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244115</t>
+          <t>245046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>276128</t>
+          <t>276632</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>197803</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>197803</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>197803</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>198324</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>198324</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>198324</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>197803</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>197803</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>197803</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>175009</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>155884</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>191660</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>25,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,41%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>160191</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>142679</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>177534</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>143238</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>178116</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>24,23%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>175009</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>158721</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>195439</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312500</t>
+          <t>311096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>360328</t>
+          <t>361833</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>92135</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78737</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>107798</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>78317</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>66446</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>93239</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>65561</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>92243</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>11,85%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>92135</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78878</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>106461</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>151377</t>
+          <t>151683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190237</t>
+          <t>190436</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>432150</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>410992</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>451184</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>61,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>422489</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>403199</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>440745</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>402912</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>442704</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>63,92%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>61,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>432150</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>411008</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>452874</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>61,8%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>824815</t>
+          <t>825590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>881227</t>
+          <t>882480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>699294</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>699294</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>699294</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>660997</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>660997</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>660997</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1052</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>699294</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>699294</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>699294</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40128</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31612</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49781</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32092</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24579</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42574</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24146</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40325</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40128</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31001</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50799</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59655</t>
+          <t>59995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84084</t>
+          <t>84400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14801</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9305</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21423</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8588</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4644</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13875</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13944</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14801</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9399</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21657</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>94769</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84101</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104189</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>63,31%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>56,18%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97348</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>86592</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>105385</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>88203</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>106251</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>70,53%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>62,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>76,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>94769</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84701</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104920</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>63,31%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>178881</t>
+          <t>178744</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>206616</t>
+          <t>205169</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>149698</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>149698</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>149698</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>138029</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>138029</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>138029</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>149698</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>149698</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>149698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70267</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59462</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81543</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>61864</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52058</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71532</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>51896</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72157</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>30,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>70267</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>59933</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>82113</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,01%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118025</t>
+          <t>115723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148867</t>
+          <t>147344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18790</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12838</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>26968</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>22389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>15467</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30423</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>16114</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>30457</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>11,07%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>18790</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>12541</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>26923</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>31985</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>52601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>130427</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>117932</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>142261</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>59,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>118075</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>106921</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>129043</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>107883</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>128855</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>58,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>130427</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>119114</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>142661</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>59,42%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231837</t>
+          <t>231290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264741</t>
+          <t>265574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>219485</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>219485</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>219485</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>202328</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>202328</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>202328</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>219485</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>219485</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>219485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4151,67 +4151,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>47363</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38629</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57807</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>28,95%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23,61%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>35,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>46857</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>39233</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>57147</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>37362</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>56449</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>30,59%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,61%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>47363</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>38988</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>56543</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>28,95%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81713</t>
+          <t>81871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107606</t>
+          <t>108162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22096</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15948</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29638</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18121</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12379</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25877</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12772</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25299</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22096</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15441</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29394</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31642</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>50611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>94144</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>83048</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104338</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>88202</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>78750</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>97320</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>78045</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>97920</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>94144</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84524</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>103888</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167684</t>
+          <t>168413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196036</t>
+          <t>196366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163603</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163603</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163603</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>153180</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>153180</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>153180</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>163603</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>163603</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>163603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>76052</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>65038</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>88368</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>60741</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50126</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72581</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>50791</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>72886</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>29,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>76052</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>63742</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>88155</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,85%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119986</t>
+          <t>120695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152529</t>
+          <t>155300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27433</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46282</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>31927</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24325</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>42469</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23968</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>40574</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>15,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>35834</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>27072</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46371</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55337</t>
+          <t>55797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82112</t>
+          <t>81116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>94478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>81518</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>106631</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>45,78%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>39,5%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>51,67%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>116151</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>103016</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>127671</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>104736</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>128559</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>55,62%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>94478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>81717</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>106848</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>45,78%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>193024</t>
+          <t>194416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228496</t>
+          <t>227858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>206364</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>206364</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>206364</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>208818</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>208818</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>208818</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>206364</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>206364</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>206364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>233811</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>212975</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>256717</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>28,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>34,73%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>201554</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>183510</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>222753</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>182794</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>222607</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>28,7%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>233811</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>214237</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>253551</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>31,63%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409343</t>
+          <t>407334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>464516</t>
+          <t>465189</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>91520</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>77898</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>107546</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>81025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68087</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>95181</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>68415</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>95817</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>11,54%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>91520</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78072</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>106403</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>12,38%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>155473</t>
+          <t>154856</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194805</t>
+          <t>194797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>413819</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>391634</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>436403</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>55,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>52,98%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>59,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>601</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>419776</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>398049</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>441660</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>395958</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>440843</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>59,77%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>56,67%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>62,88%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>413819</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>393101</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>436109</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>802786</t>
+          <t>802322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>865015</t>
+          <t>864530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>739150</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>739150</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>739150</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>702355</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>702355</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>702355</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>739150</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>739150</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>739150</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30911</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22551</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40150</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29451</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21617</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37725</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21649</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>38148</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30911</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23510</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>40660</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50473</t>
+          <t>49827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73139</t>
+          <t>72659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18488</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12114</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25529</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18260</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12651</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25458</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12114</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>14,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18488</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12281</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>26446</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27676</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47222</t>
+          <t>46046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>94712</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84837</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104319</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>65,72%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>58,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>72,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>82732</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>72980</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>91446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>72489</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>91628</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>63,42%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>94712</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84314</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>103346</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>65,72%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163198</t>
+          <t>164700</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>191634</t>
+          <t>190303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144111</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>144111</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>144111</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>130444</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>130444</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>130444</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>144111</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>144111</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>144111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40707</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31695</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50866</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>39200</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31214</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>48486</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>30906</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>48152</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>19,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40707</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31553</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50255</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68052</t>
+          <t>68357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92966</t>
+          <t>92879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37990</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>30767</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49584</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17,29%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>27719</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>20679</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>35211</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>20730</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>36399</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>13,53%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37990</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>29489</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>48336</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>54483</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77540</t>
+          <t>77724</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>141032</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>129001</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>152176</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>137984</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>127929</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>147865</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>127668</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>148712</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>67,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>141032</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>128473</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>152226</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>64,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263630</t>
+          <t>262823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294267</t>
+          <t>292944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>219728</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>219728</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>219728</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>204904</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>204904</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>204904</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>219728</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>219728</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>219728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6663,67 +6663,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>37541</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29329</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46699</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28,92%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>35442</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27514</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43672</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>27953</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45419</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>23,26%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,67%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37541</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>29555</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>47147</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>61979</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85555</t>
+          <t>85389</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25878</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18749</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34083</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24521</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18730</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32071</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17861</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32214</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>16,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25878</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18632</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>34567</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>40953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61699</t>
+          <t>61679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98059</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87713</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>108990</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>92388</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>82845</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>102169</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>83342</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>102112</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>60,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98059</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>87370</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>107540</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>60,73%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175248</t>
+          <t>177010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203477</t>
+          <t>203466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>161477</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>161477</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>161477</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152351</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152351</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152351</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>161477</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>161477</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>161477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29190</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20587</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37494</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33769</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25424</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43773</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>25576</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43935</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>16,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29190</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22235</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>38704</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76721</t>
+          <t>76420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33392</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>42606</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>37047</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>29197</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>47236</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28620</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>47810</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>18,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>33392</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25196</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>42581</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58102</t>
+          <t>57890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83963</t>
+          <t>82974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>136194</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>125004</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145675</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>68,52%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>62,89%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>73,29%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>130615</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>118253</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>140996</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>117510</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>141342</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>64,84%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>58,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>70,0%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>136194</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>124251</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>145768</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>68,52%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>248688</t>
+          <t>250738</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281231</t>
+          <t>281876</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>198776</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>198776</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>198776</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>201431</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>201431</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>201431</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>198776</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>198776</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>198776</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>138348</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>121697</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>154568</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>137863</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>121123</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>155373</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>122026</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>154970</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>20,01%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>138348</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>121841</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>155888</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>254897</t>
+          <t>253057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>300948</t>
+          <t>299968</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>115748</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>101726</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>132174</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>18,25%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>107548</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>92687</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>124248</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>94122</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>125240</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>15,61%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>115748</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>99988</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>132961</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>202845</t>
+          <t>203689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>244968</t>
+          <t>245852</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>469996</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>448422</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>489988</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>64,91%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>61,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>67,67%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>443719</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>423121</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>463199</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>421422</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>461865</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>64,39%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,21%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>469996</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>451236</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>490771</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>886026</t>
+          <t>887016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>944300</t>
+          <t>944614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>724092</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1038</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>689130</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>689130</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>689130</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>724092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
